--- a/doc/IPRouter.xlsx
+++ b/doc/IPRouter.xlsx
@@ -1,28 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\proj\OpenKNX\_IP-Router\OAM-IP-Router\doc\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6678478-6A65-4C2F-B4E0-3D27934DE289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="75" windowWidth="30600" windowHeight="13200" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
     <sheet name="ToDo" sheetId="2" r:id="rId2"/>
     <sheet name="knxprod - prop" sheetId="3" r:id="rId3"/>
     <sheet name="Tabelle2" sheetId="4" r:id="rId4"/>
+    <sheet name="Tabelle3" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>dosp</author>
   </authors>
   <commentList>
-    <comment ref="M20" authorId="0">
+    <comment ref="M20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -36,7 +43,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N20" authorId="0">
+    <comment ref="N20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -50,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O20" authorId="0">
+    <comment ref="O20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
@@ -64,7 +71,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P20" authorId="0">
+    <comment ref="P20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
       <text>
         <r>
           <rPr>
@@ -78,7 +85,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J25" authorId="0">
+    <comment ref="J25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
       <text>
         <r>
           <rPr>
@@ -93,7 +100,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L25" authorId="0">
+    <comment ref="L25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
       <text>
         <r>
           <rPr>
@@ -107,7 +114,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N25" authorId="0">
+    <comment ref="N25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
       <text>
         <r>
           <rPr>
@@ -121,7 +128,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P25" authorId="0">
+    <comment ref="P25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
       <text>
         <r>
           <rPr>
@@ -135,7 +142,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M30" authorId="0">
+    <comment ref="M30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
       <text>
         <r>
           <rPr>
@@ -149,7 +156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N30" authorId="0">
+    <comment ref="N30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -163,7 +170,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P30" authorId="0">
+    <comment ref="P30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -177,7 +184,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N36" authorId="0">
+    <comment ref="N36" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -191,7 +198,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P36" authorId="0">
+    <comment ref="P36" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -210,7 +217,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="119">
   <si>
     <t>W5500</t>
   </si>
@@ -635,13 +642,297 @@
   </si>
   <si>
     <t>LL =&gt; NL =&gt; LL</t>
+  </si>
+  <si>
+    <r>
+      <t>TpUartDataLinkLayer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>processRxFrame</t>
+    </r>
+  </si>
+  <si>
+    <t>eingehender Frame auf TP</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  DataLinkLayer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>frameReceived</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    _cemiServer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>-&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>dataIndicationToTunnel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>frame</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    _networkLayerEntity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>broadcastIndication</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    _networkLayerEntity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>systemBroadcastIndication</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    NetworkLayerEntity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>dataIndication</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      NetworkLayerCoupler</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>dataIndication</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">      ?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        NetworkLayerCoupler</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>routeDataIndividual</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        NetworkLayerCoupler</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>sendMsgHopCount</t>
+    </r>
+  </si>
+  <si>
+    <t>only Unicast</t>
+  </si>
+  <si>
+    <t>only Multicast</t>
+  </si>
+  <si>
+    <r>
+      <t>IpDataLinkLayer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>loop</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>()</t>
+    </r>
+  </si>
+  <si>
+    <t>eingehender Frame auf IP</t>
+  </si>
+  <si>
+    <t>wenn interfaceIdx=1 (=secondary interface / TP)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="11" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -712,8 +1003,27 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9CDCFE"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -780,8 +1090,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -903,11 +1219,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color theme="1" tint="0.499984740745262"/>
+      </left>
+      <right style="hair">
+        <color theme="1" tint="0.499984740745262"/>
+      </right>
+      <top style="hair">
+        <color theme="1" tint="0.499984740745262"/>
+      </top>
+      <bottom style="hair">
+        <color theme="1" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -942,9 +1273,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -964,6 +1292,33 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -997,33 +1352,20 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1038,6 +1380,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1060,7 +1405,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Grafik 1"/>
+        <xdr:cNvPr id="2" name="Grafik 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1103,7 +1454,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Grafik 1"/>
+        <xdr:cNvPr id="2" name="Grafik 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -1158,7 +1515,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Grafik 3"/>
+        <xdr:cNvPr id="4" name="Grafik 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -1213,7 +1576,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Grafik 4"/>
+        <xdr:cNvPr id="5" name="Grafik 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -1257,9 +1626,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Larissa">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Larissa">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1297,7 +1666,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Larissa">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1369,7 +1738,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Larissa">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1542,7 +1911,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="D5:V37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1675,7 +2044,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="C5:H49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1892,7 +2261,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="F13:R36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2016,26 +2385,26 @@
       <c r="I19" t="s">
         <v>62</v>
       </c>
-      <c r="J19" s="37" t="s">
+      <c r="J19" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="K19" s="38"/>
+      <c r="K19" s="27"/>
       <c r="L19" s="11">
         <v>1</v>
       </c>
-      <c r="M19" s="12">
+      <c r="M19" s="11">
         <v>1</v>
       </c>
       <c r="N19" s="11">
         <v>0</v>
       </c>
-      <c r="O19" s="12">
+      <c r="O19" s="11">
         <v>1</v>
       </c>
-      <c r="P19" s="37" t="s">
+      <c r="P19" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="Q19" s="38"/>
+      <c r="Q19" s="27"/>
     </row>
     <row r="20" spans="6:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I20" t="s">
@@ -2044,19 +2413,19 @@
       <c r="J20" s="10"/>
       <c r="K20" s="10"/>
       <c r="L20" s="10"/>
-      <c r="M20" s="18">
+      <c r="M20" s="17">
         <v>8</v>
       </c>
-      <c r="N20" s="18">
+      <c r="N20" s="17">
         <v>9</v>
       </c>
-      <c r="O20" s="18">
+      <c r="O20" s="17">
         <v>10</v>
       </c>
-      <c r="P20" s="35">
+      <c r="P20" s="24">
         <v>11</v>
       </c>
-      <c r="Q20" s="36"/>
+      <c r="Q20" s="25"/>
       <c r="R20" t="s">
         <v>65</v>
       </c>
@@ -2101,10 +2470,10 @@
       <c r="I24" t="s">
         <v>62</v>
       </c>
-      <c r="J24" s="37" t="s">
+      <c r="J24" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="K24" s="38"/>
+      <c r="K24" s="27"/>
       <c r="L24" s="11">
         <v>1</v>
       </c>
@@ -2117,31 +2486,31 @@
       <c r="O24" s="11">
         <v>1</v>
       </c>
-      <c r="P24" s="37" t="s">
+      <c r="P24" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="Q24" s="38"/>
+      <c r="Q24" s="27"/>
     </row>
     <row r="25" spans="6:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I25" t="s">
         <v>59</v>
       </c>
-      <c r="J25" s="31">
+      <c r="J25" s="20">
         <v>2</v>
       </c>
-      <c r="K25" s="32"/>
-      <c r="L25" s="19">
+      <c r="K25" s="21"/>
+      <c r="L25" s="18">
         <v>3</v>
       </c>
       <c r="M25" s="10"/>
-      <c r="N25" s="19">
+      <c r="N25" s="18">
         <v>4</v>
       </c>
       <c r="O25" s="10"/>
-      <c r="P25" s="33">
+      <c r="P25" s="22">
         <v>5</v>
       </c>
-      <c r="Q25" s="34"/>
+      <c r="Q25" s="23"/>
       <c r="R25" t="s">
         <v>66</v>
       </c>
@@ -2186,22 +2555,22 @@
       <c r="I29" t="s">
         <v>58</v>
       </c>
-      <c r="J29" s="27" t="s">
+      <c r="J29" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="K29" s="27"/>
-      <c r="L29" s="27"/>
+      <c r="K29" s="35"/>
+      <c r="L29" s="35"/>
       <c r="M29" s="11">
         <v>1</v>
       </c>
-      <c r="N29" s="26" t="s">
+      <c r="N29" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="O29" s="24"/>
-      <c r="P29" s="24" t="s">
+      <c r="O29" s="32"/>
+      <c r="P29" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="Q29" s="25"/>
+      <c r="Q29" s="33"/>
     </row>
     <row r="30" spans="6:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I30" t="s">
@@ -2210,17 +2579,17 @@
       <c r="J30" s="10"/>
       <c r="K30" s="10"/>
       <c r="L30" s="10"/>
-      <c r="M30" s="39">
+      <c r="M30" s="19">
         <v>12</v>
       </c>
-      <c r="N30" s="30">
+      <c r="N30" s="38">
         <v>13</v>
       </c>
-      <c r="O30" s="28"/>
-      <c r="P30" s="28">
+      <c r="O30" s="36"/>
+      <c r="P30" s="36">
         <v>14</v>
       </c>
-      <c r="Q30" s="29"/>
+      <c r="Q30" s="37"/>
       <c r="R30" t="s">
         <v>65</v>
       </c>
@@ -2275,52 +2644,45 @@
       <c r="I35" t="s">
         <v>58</v>
       </c>
-      <c r="J35" s="27" t="s">
+      <c r="J35" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="K35" s="27"/>
-      <c r="L35" s="27"/>
+      <c r="K35" s="35"/>
+      <c r="L35" s="35"/>
       <c r="M35" s="11">
         <v>1</v>
       </c>
-      <c r="N35" s="26" t="s">
+      <c r="N35" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="O35" s="24"/>
-      <c r="P35" s="24" t="s">
+      <c r="O35" s="32"/>
+      <c r="P35" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="Q35" s="25"/>
+      <c r="Q35" s="33"/>
     </row>
     <row r="36" spans="6:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I36" t="s">
         <v>60</v>
       </c>
-      <c r="J36" s="23"/>
-      <c r="K36" s="23"/>
-      <c r="L36" s="23"/>
+      <c r="J36" s="31"/>
+      <c r="K36" s="31"/>
+      <c r="L36" s="31"/>
       <c r="M36" s="10"/>
-      <c r="N36" s="20">
+      <c r="N36" s="28">
         <v>6</v>
       </c>
-      <c r="O36" s="21"/>
-      <c r="P36" s="21">
+      <c r="O36" s="29"/>
+      <c r="P36" s="29">
         <v>7</v>
       </c>
-      <c r="Q36" s="22"/>
+      <c r="Q36" s="30"/>
       <c r="R36" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="P25:Q25"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="J24:K24"/>
     <mergeCell ref="N36:O36"/>
     <mergeCell ref="P36:Q36"/>
     <mergeCell ref="J36:L36"/>
@@ -2332,6 +2694,13 @@
     <mergeCell ref="J35:L35"/>
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="J24:K24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -2341,7 +2710,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B3:P24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2358,7 +2727,7 @@
       <c r="C3" t="s">
         <v>89</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="16" t="s">
         <v>96</v>
       </c>
       <c r="J3" t="s">
@@ -2372,10 +2741,10 @@
       <c r="C4" t="s">
         <v>91</v>
       </c>
-      <c r="H4" s="14"/>
+      <c r="H4" s="13"/>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="H5" s="14"/>
+      <c r="H5" s="13"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
@@ -2384,37 +2753,37 @@
       <c r="C6" t="s">
         <v>102</v>
       </c>
-      <c r="H6" s="14"/>
+      <c r="H6" s="13"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="H7" s="14"/>
+      <c r="H7" s="13"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="H8" s="14"/>
+      <c r="H8" s="13"/>
       <c r="L8" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="H9" s="16"/>
+      <c r="H9" s="15"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
         <v>99</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="H10" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="I10" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="J10" s="13" t="s">
+      <c r="J10" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="K10" s="13" t="s">
+      <c r="K10" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="L10" s="13" t="s">
+      <c r="L10" s="12" t="s">
         <v>74</v>
       </c>
     </row>
@@ -2425,41 +2794,41 @@
       <c r="G11" t="s">
         <v>87</v>
       </c>
-      <c r="H11" s="13" t="s">
+      <c r="H11" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I11" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="J11" s="13" t="s">
+      <c r="J11" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="L11" s="13" t="s">
+      <c r="L11" s="12" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="H12" s="14"/>
-      <c r="J12" s="13" t="s">
+      <c r="H12" s="13"/>
+      <c r="J12" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="K12" s="14"/>
-      <c r="L12" s="13" t="s">
+      <c r="K12" s="13"/>
+      <c r="L12" s="12" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="H13" s="14"/>
-      <c r="I13" s="13" t="s">
+      <c r="H13" s="13"/>
+      <c r="I13" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="K13" s="13" t="s">
+      <c r="K13" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="L13" s="13" t="s">
+      <c r="L13" s="12" t="s">
         <v>74</v>
       </c>
     </row>
@@ -2470,16 +2839,16 @@
       <c r="G14" t="s">
         <v>87</v>
       </c>
-      <c r="H14" s="13" t="s">
+      <c r="H14" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="J14" s="13" t="s">
+      <c r="J14" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="K14" s="13" t="s">
+      <c r="K14" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="L14" s="13" t="s">
+      <c r="L14" s="12" t="s">
         <v>74</v>
       </c>
     </row>
@@ -2490,34 +2859,34 @@
       <c r="G15" t="s">
         <v>87</v>
       </c>
-      <c r="H15" s="13" t="s">
+      <c r="H15" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="J15" s="13" t="s">
+      <c r="J15" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="K15" s="13" t="s">
+      <c r="K15" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="L15" s="13" t="s">
+      <c r="L15" s="12" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="H16" s="14"/>
+      <c r="H16" s="13"/>
     </row>
     <row r="17" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D17" t="s">
         <v>99</v>
       </c>
-      <c r="H17" s="16" t="s">
+      <c r="H17" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="J17" s="15" t="s">
+      <c r="J17" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="K17" s="14"/>
-      <c r="L17" s="13" t="s">
+      <c r="K17" s="13"/>
+      <c r="L17" s="12" t="s">
         <v>74</v>
       </c>
     </row>
@@ -2525,14 +2894,14 @@
       <c r="D18" t="s">
         <v>99</v>
       </c>
-      <c r="H18" s="16" t="s">
+      <c r="H18" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="J18" s="15" t="s">
+      <c r="J18" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="K18" s="14"/>
-      <c r="L18" s="13" t="s">
+      <c r="K18" s="13"/>
+      <c r="L18" s="12" t="s">
         <v>74</v>
       </c>
     </row>
@@ -2540,48 +2909,156 @@
       <c r="D19" t="s">
         <v>99</v>
       </c>
-      <c r="H19" s="16" t="s">
+      <c r="H19" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="J19" s="15" t="s">
+      <c r="J19" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="K19" s="14"/>
-      <c r="L19" s="13" t="s">
+      <c r="K19" s="13"/>
+      <c r="L19" s="12" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="20" spans="4:16" x14ac:dyDescent="0.25">
-      <c r="L20" s="13"/>
-      <c r="M20" s="14"/>
-      <c r="P20" s="13"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="13"/>
+      <c r="P20" s="12"/>
     </row>
     <row r="21" spans="4:16" x14ac:dyDescent="0.25">
-      <c r="L21" s="13"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
-      <c r="P21" s="13"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="P21" s="12"/>
     </row>
     <row r="22" spans="4:16" x14ac:dyDescent="0.25">
-      <c r="L22" s="15"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
-      <c r="P22" s="13"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="P22" s="12"/>
     </row>
     <row r="23" spans="4:16" x14ac:dyDescent="0.25">
-      <c r="L23" s="15"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
-      <c r="P23" s="13"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+      <c r="P23" s="12"/>
     </row>
     <row r="24" spans="4:16" x14ac:dyDescent="0.25">
-      <c r="L24" s="15"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="P24" s="13"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="P24" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0B16AAA-981A-4547-A056-1AF9B3AE4D24}">
+  <dimension ref="B6:E20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="50" style="41" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.28515625" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="62.140625" style="44" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C6" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="D6" s="44" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B7" s="42"/>
+      <c r="C7" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" s="44" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8" s="42"/>
+      <c r="C8" s="42" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="43"/>
+      <c r="C9" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" s="44" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C10" s="40" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C11" s="40" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C12" s="40" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C13" s="40" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C14" s="39" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C15" s="39" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C16" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C17" s="39"/>
+    </row>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C18" s="39"/>
+    </row>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C19" s="39"/>
+    </row>
+    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C20" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20" s="44" t="s">
+        <v>115</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{9d258917-277f-42cd-a3cd-14c4e9ee58bc}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>